--- a/春大直_報修統計_2026.xlsx
+++ b/春大直_報修統計_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d14d3036a2a384b/_Ragic/portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CE5EFA-3864-4D41-A04C-5B3D6552C2DE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AC74392-11EF-4CDF-99C6-88AB694D6825}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30600" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.1 報修統計" sheetId="1" r:id="rId1"/>
@@ -1970,13 +1970,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2012,6 +2005,13 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2285,22 +2285,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2750,22 +2750,22 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2780,6 +2780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V93"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -2912,7 +2913,7 @@
       </c>
       <c r="V2" s="32"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" hidden="1">
       <c r="A3" s="33" t="s">
         <v>55</v>
       </c>
@@ -3020,7 +3021,7 @@
       </c>
       <c r="V4" s="32"/>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" hidden="1">
       <c r="A5" s="33" t="s">
         <v>69</v>
       </c>
@@ -3078,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" hidden="1">
       <c r="A6" s="30" t="s">
         <v>74</v>
       </c>
@@ -3138,7 +3139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" hidden="1">
       <c r="A7" s="33" t="s">
         <v>81</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" hidden="1">
       <c r="A8" s="30" t="s">
         <v>84</v>
       </c>
@@ -3258,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" hidden="1">
       <c r="A9" s="33" t="s">
         <v>90</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" hidden="1">
       <c r="A10" s="30" t="s">
         <v>95</v>
       </c>
@@ -3480,7 +3481,7 @@
       </c>
       <c r="V12" s="32"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" hidden="1">
       <c r="A13" s="33" t="s">
         <v>107</v>
       </c>
@@ -3540,7 +3541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" hidden="1">
       <c r="A14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3694,7 +3695,7 @@
       </c>
       <c r="V16" s="32"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" hidden="1">
       <c r="A17" s="33" t="s">
         <v>128</v>
       </c>
@@ -3754,7 +3755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" hidden="1">
       <c r="A18" s="30" t="s">
         <v>133</v>
       </c>
@@ -3810,7 +3811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" hidden="1">
       <c r="A19" s="33" t="s">
         <v>138</v>
       </c>
@@ -3866,7 +3867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" hidden="1">
       <c r="A20" s="30" t="s">
         <v>143</v>
       </c>
@@ -3920,7 +3921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" hidden="1">
       <c r="A21" s="33" t="s">
         <v>148</v>
       </c>
@@ -3976,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" hidden="1">
       <c r="A22" s="30" t="s">
         <v>153</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" hidden="1">
       <c r="A23" s="33" t="s">
         <v>158</v>
       </c>
@@ -4088,7 +4089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" hidden="1">
       <c r="A24" s="30" t="s">
         <v>162</v>
       </c>
@@ -4142,7 +4143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" hidden="1">
       <c r="A25" s="33" t="s">
         <v>167</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" hidden="1">
       <c r="A26" s="30" t="s">
         <v>171</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" hidden="1">
       <c r="A27" s="33" t="s">
         <v>175</v>
       </c>
@@ -4316,7 +4317,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" hidden="1">
       <c r="A28" s="30" t="s">
         <v>180</v>
       </c>
@@ -4372,7 +4373,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" hidden="1">
       <c r="A29" s="33" t="s">
         <v>186</v>
       </c>
@@ -4426,7 +4427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" hidden="1">
       <c r="A30" s="30" t="s">
         <v>191</v>
       </c>
@@ -4480,7 +4481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" hidden="1">
       <c r="A31" s="33" t="s">
         <v>195</v>
       </c>
@@ -4538,7 +4539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" hidden="1">
       <c r="A32" s="30" t="s">
         <v>200</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" hidden="1">
       <c r="A33" s="33" t="s">
         <v>204</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" hidden="1">
       <c r="A34" s="30" t="s">
         <v>208</v>
       </c>
@@ -4708,7 +4709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" hidden="1">
       <c r="A35" s="33" t="s">
         <v>213</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" hidden="1">
       <c r="A36" s="30" t="s">
         <v>217</v>
       </c>
@@ -4820,7 +4821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" hidden="1">
       <c r="A37" s="33" t="s">
         <v>222</v>
       </c>
@@ -4880,7 +4881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" hidden="1">
       <c r="A38" s="30" t="s">
         <v>227</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" hidden="1">
       <c r="A39" s="33" t="s">
         <v>232</v>
       </c>
@@ -4996,7 +4997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" hidden="1">
       <c r="A40" s="30" t="s">
         <v>237</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" hidden="1">
       <c r="A41" s="33" t="s">
         <v>241</v>
       </c>
@@ -5110,7 +5111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" hidden="1">
       <c r="A42" s="30" t="s">
         <v>245</v>
       </c>
@@ -5166,7 +5167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" hidden="1">
       <c r="A43" s="33" t="s">
         <v>250</v>
       </c>
@@ -5220,7 +5221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" hidden="1">
       <c r="A44" s="30" t="s">
         <v>254</v>
       </c>
@@ -5282,7 +5283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" hidden="1">
       <c r="A45" s="33" t="s">
         <v>259</v>
       </c>
@@ -5340,7 +5341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" hidden="1">
       <c r="A46" s="30" t="s">
         <v>263</v>
       </c>
@@ -5400,7 +5401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" hidden="1">
       <c r="A47" s="33" t="s">
         <v>267</v>
       </c>
@@ -5460,7 +5461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" hidden="1">
       <c r="A48" s="30" t="s">
         <v>271</v>
       </c>
@@ -5518,7 +5519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" hidden="1">
       <c r="A49" s="33" t="s">
         <v>276</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" hidden="1">
       <c r="A50" s="30" t="s">
         <v>281</v>
       </c>
@@ -5640,7 +5641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" hidden="1">
       <c r="A51" s="33" t="s">
         <v>285</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" hidden="1">
       <c r="A52" s="30" t="s">
         <v>290</v>
       </c>
@@ -5756,7 +5757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" hidden="1">
       <c r="A53" s="33" t="s">
         <v>293</v>
       </c>
@@ -5908,7 +5909,7 @@
       </c>
       <c r="V55" s="32"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" hidden="1">
       <c r="A56" s="30" t="s">
         <v>300</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" hidden="1">
       <c r="A57" s="33" t="s">
         <v>303</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" hidden="1">
       <c r="A58" s="30" t="s">
         <v>307</v>
       </c>
@@ -6094,7 +6095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" hidden="1">
       <c r="A59" s="33" t="s">
         <v>310</v>
       </c>
@@ -6204,7 +6205,7 @@
       </c>
       <c r="V60" s="32"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" hidden="1">
       <c r="A61" s="33" t="s">
         <v>317</v>
       </c>
@@ -6264,7 +6265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" hidden="1">
       <c r="A62" s="30" t="s">
         <v>320</v>
       </c>
@@ -6322,7 +6323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" hidden="1">
       <c r="A63" s="33" t="s">
         <v>325</v>
       </c>
@@ -6384,7 +6385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" hidden="1">
       <c r="A64" s="30" t="s">
         <v>328</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" hidden="1">
       <c r="A65" s="33" t="s">
         <v>333</v>
       </c>
@@ -6504,7 +6505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" hidden="1">
       <c r="A66" s="30" t="s">
         <v>336</v>
       </c>
@@ -6562,7 +6563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" hidden="1">
       <c r="A67" s="33" t="s">
         <v>340</v>
       </c>
@@ -6672,7 +6673,7 @@
       </c>
       <c r="V68" s="32"/>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" hidden="1">
       <c r="A69" s="33" t="s">
         <v>348</v>
       </c>
@@ -6732,7 +6733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" hidden="1">
       <c r="A70" s="30" t="s">
         <v>350</v>
       </c>
@@ -6838,7 +6839,7 @@
       </c>
       <c r="V71" s="32"/>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" hidden="1">
       <c r="A72" s="30" t="s">
         <v>358</v>
       </c>
@@ -6992,7 +6993,7 @@
       </c>
       <c r="V74" s="32"/>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" hidden="1">
       <c r="A75" s="33" t="s">
         <v>367</v>
       </c>
@@ -7052,7 +7053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" hidden="1">
       <c r="A76" s="30" t="s">
         <v>370</v>
       </c>
@@ -7112,7 +7113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" hidden="1">
       <c r="A77" s="33" t="s">
         <v>374</v>
       </c>
@@ -7166,7 +7167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" hidden="1">
       <c r="A78" s="30" t="s">
         <v>377</v>
       </c>
@@ -7222,7 +7223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" hidden="1">
       <c r="A79" s="33" t="s">
         <v>382</v>
       </c>
@@ -7276,7 +7277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" hidden="1">
       <c r="A80" s="30" t="s">
         <v>385</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" hidden="1">
       <c r="A81" s="33" t="s">
         <v>389</v>
       </c>
@@ -7438,7 +7439,7 @@
       </c>
       <c r="V82" s="32"/>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" hidden="1">
       <c r="A83" s="33" t="s">
         <v>396</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" hidden="1">
       <c r="A84" s="30" t="s">
         <v>401</v>
       </c>
@@ -7546,7 +7547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:22" hidden="1">
       <c r="A85" s="33" t="s">
         <v>405</v>
       </c>
@@ -7662,7 +7663,7 @@
       </c>
       <c r="V86" s="32"/>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:22" hidden="1">
       <c r="A87" s="33" t="s">
         <v>417</v>
       </c>
@@ -7720,7 +7721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" hidden="1">
       <c r="A88" s="30" t="s">
         <v>421</v>
       </c>
@@ -7882,7 +7883,7 @@
       </c>
       <c r="V90" s="32"/>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" hidden="1">
       <c r="A91" s="33" t="s">
         <v>434</v>
       </c>
@@ -7950,7 +7951,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V91" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:V91" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="14">
+      <filters>
+        <filter val="✗"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7961,1361 +7968,1361 @@
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.21875" style="42" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" style="42"/>
-    <col min="4" max="4" width="13.21875" style="42" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="8.88671875" style="42"/>
-    <col min="11" max="11" width="11.21875" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.21875" style="39" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="39"/>
+    <col min="4" max="4" width="13.21875" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="8.88671875" style="39"/>
+    <col min="11" max="11" width="11.21875" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="36" t="s">
         <v>439</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="36" t="s">
         <v>440</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="38" t="s">
         <v>441</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="38" t="s">
         <v>442</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="36" t="s">
         <v>443</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="36" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="41" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="42">
         <v>46131.898611111108</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="K2" s="42" t="str">
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="K2" s="39" t="str">
         <f>VLOOKUP(A2,原始數據!A:A,1,0)</f>
         <v>202604-028</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="45">
+      <c r="C3" s="40"/>
+      <c r="D3" s="42">
         <v>46131.821527777778</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="K3" s="42" t="str">
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="K3" s="39" t="str">
         <f>VLOOKUP(A3,原始數據!A:A,1,0)</f>
         <v>202604-027</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="42">
         <v>46131.612500000003</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="44" t="s">
         <v>447</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="45">
         <v>38</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="K4" s="42" t="str">
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="K4" s="39" t="str">
         <f>VLOOKUP(A4,原始數據!A:A,1,0)</f>
         <v>202604-026</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="41" t="s">
         <v>305</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="42">
         <v>46130.85</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="44" t="s">
         <v>448</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="K5" s="42" t="str">
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="K5" s="39" t="str">
         <f>VLOOKUP(A5,原始數據!A:A,1,0)</f>
         <v>202604-025</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="41" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="42">
         <v>46130.741666666669</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="44" t="s">
         <v>449</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="K6" s="42" t="str">
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="K6" s="39" t="str">
         <f>VLOOKUP(A6,原始數據!A:A,1,0)</f>
         <v>202604-024</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="40" t="s">
         <v>310</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="42">
         <v>46129.45416666667</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="44" t="s">
         <v>450</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="45">
         <v>142</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="K7" s="42" t="str">
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="K7" s="39" t="str">
         <f>VLOOKUP(A7,原始數據!A:A,1,0)</f>
         <v>202604-023</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="42">
         <v>46128.829861111109</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="K8" s="42" t="str">
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="K8" s="39" t="str">
         <f>VLOOKUP(A8,原始數據!A:A,1,0)</f>
         <v>202604-022</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="42">
         <v>46128.661805555559</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="44" t="s">
         <v>447</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="K9" s="42" t="str">
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="K9" s="39" t="str">
         <f>VLOOKUP(A9,原始數據!A:A,1,0)</f>
         <v>202604-021</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="42">
         <v>46127.70208333333</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="44" t="s">
         <v>451</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="K10" s="42" t="str">
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="K10" s="39" t="str">
         <f>VLOOKUP(A10,原始數據!A:A,1,0)</f>
         <v>202604-020</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" thickBot="1">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>46127.490277777775</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="44" t="s">
         <v>453</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="45">
         <v>1600</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="46" t="s">
         <v>454</v>
       </c>
-      <c r="I11" s="43"/>
-      <c r="K11" s="42" t="str">
+      <c r="I11" s="40"/>
+      <c r="K11" s="39" t="str">
         <f>VLOOKUP(A11,原始數據!A:A,1,0)</f>
         <v>202604-019</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="42">
         <v>46125.628472222219</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="44" t="s">
         <v>455</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="K12" s="42" t="str">
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="K12" s="39" t="str">
         <f>VLOOKUP(A12,原始數據!A:A,1,0)</f>
         <v>202604-018</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="42">
         <v>46125.431944444441</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="K13" s="42" t="str">
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="K13" s="39" t="str">
         <f>VLOOKUP(A13,原始數據!A:A,1,0)</f>
         <v>202604-017</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="45">
+      <c r="C14" s="40"/>
+      <c r="D14" s="42">
         <v>46124.82708333333</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="K14" s="42" t="str">
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="K14" s="39" t="str">
         <f>VLOOKUP(A14,原始數據!A:A,1,0)</f>
         <v>202604-016</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" thickBot="1">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="42">
         <v>46124.824999999997</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="44" t="s">
         <v>458</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="K15" s="42" t="str">
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="K15" s="39" t="str">
         <f>VLOOKUP(A15,原始數據!A:A,1,0)</f>
         <v>202604-015</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="42">
         <v>46122.6875</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="44" t="s">
         <v>460</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="K16" s="42" t="str">
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="K16" s="39" t="str">
         <f>VLOOKUP(A16,原始數據!A:A,1,0)</f>
         <v>202604-014</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" thickBot="1">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="41" t="s">
         <v>349</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="42">
         <v>46122.686805555553</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="44" t="s">
         <v>461</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="K17" s="42" t="str">
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="K17" s="39" t="str">
         <f>VLOOKUP(A17,原始數據!A:A,1,0)</f>
         <v>202604-013</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="42">
         <v>46122.685416666667</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="44" t="s">
         <v>462</v>
       </c>
-      <c r="G18" s="47" t="s">
+      <c r="G18" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="K18" s="42" t="str">
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="K18" s="39" t="str">
         <f>VLOOKUP(A18,原始數據!A:A,1,0)</f>
         <v>202604-012</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="42">
         <v>46122.684027777781</v>
       </c>
-      <c r="E19" s="46" t="s">
+      <c r="E19" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="F19" s="44" t="s">
         <v>464</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G19" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="K19" s="42" t="str">
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="K19" s="39" t="str">
         <f>VLOOKUP(A19,原始數據!A:A,1,0)</f>
         <v>202604-011</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="41" t="s">
         <v>359</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="42">
         <v>46122.683333333334</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="E20" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="44" t="s">
         <v>465</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="K20" s="42" t="str">
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="K20" s="39" t="str">
         <f>VLOOKUP(A20,原始數據!A:A,1,0)</f>
         <v>202604-010</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="42">
         <v>46122.681250000001</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="44" t="s">
         <v>466</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="K21" s="42" t="str">
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="K21" s="39" t="str">
         <f>VLOOKUP(A21,原始數據!A:A,1,0)</f>
         <v>202604-009</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="42">
         <v>46122.677083333336</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="K22" s="42" t="str">
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="K22" s="39" t="str">
         <f>VLOOKUP(A22,原始數據!A:A,1,0)</f>
         <v>202604-008</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="41" t="s">
         <v>368</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="42">
         <v>46122.456944444442</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="44" t="s">
         <v>468</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="45">
         <v>137</v>
       </c>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="K23" s="42" t="str">
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="K23" s="39" t="str">
         <f>VLOOKUP(A23,原始數據!A:A,1,0)</f>
         <v>202604-007</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="41" t="s">
         <v>372</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="45">
+      <c r="D24" s="42">
         <v>46119.581250000003</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="44" t="s">
         <v>469</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="45">
         <v>499</v>
       </c>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="K24" s="42" t="str">
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="K24" s="39" t="str">
         <f>VLOOKUP(A24,原始數據!A:A,1,0)</f>
         <v>202604-006</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="45">
+      <c r="C25" s="40"/>
+      <c r="D25" s="42">
         <v>46118.46875</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="44" t="s">
         <v>470</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="G25" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="K25" s="42" t="str">
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="K25" s="39" t="str">
         <f>VLOOKUP(A25,原始數據!A:A,1,0)</f>
         <v>202604-005</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="41" t="s">
         <v>379</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="45">
+      <c r="C26" s="40"/>
+      <c r="D26" s="42">
         <v>46117.4375</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="44" t="s">
         <v>471</v>
       </c>
-      <c r="G26" s="48">
+      <c r="G26" s="45">
         <v>137</v>
       </c>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="K26" s="42" t="str">
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="K26" s="39" t="str">
         <f>VLOOKUP(A26,原始數據!A:A,1,0)</f>
         <v>202604-004</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" thickBot="1">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="41" t="s">
         <v>384</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="45">
+      <c r="C27" s="40"/>
+      <c r="D27" s="42">
         <v>46116.890277777777</v>
       </c>
-      <c r="E27" s="46" t="s">
+      <c r="E27" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="44" t="s">
         <v>472</v>
       </c>
-      <c r="G27" s="47" t="s">
+      <c r="G27" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="K27" s="42" t="str">
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="K27" s="39" t="str">
         <f>VLOOKUP(A27,原始數據!A:A,1,0)</f>
         <v>202604-003</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="41" t="s">
         <v>387</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="45">
+      <c r="D28" s="42">
         <v>46114.634722222225</v>
       </c>
-      <c r="E28" s="46" t="s">
+      <c r="E28" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="44" t="s">
         <v>455</v>
       </c>
-      <c r="G28" s="47" t="s">
+      <c r="G28" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="K28" s="42" t="str">
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="K28" s="39" t="str">
         <f>VLOOKUP(A28,原始數據!A:A,1,0)</f>
         <v>202604-002</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B29" s="44" t="s">
+      <c r="B29" s="41" t="s">
         <v>391</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="45">
+      <c r="D29" s="42">
         <v>46114.477083333331</v>
       </c>
-      <c r="E29" s="46" t="s">
+      <c r="E29" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="G29" s="48">
+      <c r="G29" s="45">
         <v>31300</v>
       </c>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="K29" s="42" t="str">
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="K29" s="39" t="str">
         <f>VLOOKUP(A29,原始數據!A:A,1,0)</f>
         <v>202604-001</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="43" t="s">
+      <c r="A30" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="B30" s="44" t="s">
+      <c r="B30" s="41" t="s">
         <v>294</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="45">
+      <c r="D30" s="42">
         <v>46132.445138888892</v>
       </c>
-      <c r="E30" s="46" t="s">
+      <c r="E30" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="44" t="s">
         <v>474</v>
       </c>
-      <c r="G30" s="47" t="s">
+      <c r="G30" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="K30" s="42" t="str">
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="K30" s="39" t="str">
         <f>VLOOKUP(A30,原始數據!A:A,1,0)</f>
         <v>202604-029</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="C31" s="43" t="s">
+      <c r="C31" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="45">
+      <c r="D31" s="42">
         <v>46132.79791666667</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="44" t="s">
         <v>475</v>
       </c>
-      <c r="G31" s="47" t="s">
+      <c r="G31" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="K31" s="42" t="str">
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="K31" s="39" t="str">
         <f>VLOOKUP(A31,原始數據!A:A,1,0)</f>
         <v>202604-031</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="41" t="s">
         <v>291</v>
       </c>
-      <c r="C32" s="43" t="s">
+      <c r="C32" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="45">
+      <c r="D32" s="42">
         <v>46132.790277777778</v>
       </c>
-      <c r="E32" s="46" t="s">
+      <c r="E32" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="44" t="s">
         <v>475</v>
       </c>
-      <c r="G32" s="47" t="s">
+      <c r="G32" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="K32" s="42" t="str">
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="K32" s="39" t="str">
         <f>VLOOKUP(A32,原始數據!A:A,1,0)</f>
         <v>202604-030</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" thickBot="1">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="C33" s="43" t="s">
+      <c r="C33" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="45">
+      <c r="D33" s="42">
         <v>46133.688888888886</v>
       </c>
-      <c r="E33" s="46" t="s">
+      <c r="E33" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="44" t="s">
         <v>476</v>
       </c>
-      <c r="G33" s="47" t="s">
+      <c r="G33" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="K33" s="42" t="str">
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="K33" s="39" t="str">
         <f>VLOOKUP(A33,原始數據!A:A,1,0)</f>
         <v>202604-032</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="44" t="s">
+      <c r="B34" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="45">
+      <c r="C34" s="40"/>
+      <c r="D34" s="42">
         <v>46134.418749999997</v>
       </c>
-      <c r="E34" s="46" t="s">
+      <c r="E34" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="G34" s="47" t="s">
+      <c r="G34" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="K34" s="42" t="str">
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="K34" s="39" t="str">
         <f>VLOOKUP(A34,原始數據!A:A,1,0)</f>
         <v>202604-033</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" thickBot="1">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="42">
         <v>46134.438194444447</v>
       </c>
-      <c r="E35" s="46" t="s">
+      <c r="E35" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="G35" s="47" t="s">
+      <c r="G35" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="K35" s="42" t="str">
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="K35" s="39" t="str">
         <f>VLOOKUP(A35,原始數據!A:A,1,0)</f>
         <v>202604-034</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="44" t="s">
+      <c r="B36" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C36" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="42">
         <v>46135.595833333333</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="F36" s="47" t="s">
+      <c r="F36" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="G36" s="47" t="s">
+      <c r="G36" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="K36" s="42" t="str">
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="K36" s="39" t="str">
         <f>VLOOKUP(A36,原始數據!A:A,1,0)</f>
         <v>202604-036</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" thickBot="1">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B37" s="44" t="s">
+      <c r="B37" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="43" t="s">
+      <c r="C37" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="45">
+      <c r="D37" s="42">
         <v>46135.59652777778</v>
       </c>
-      <c r="E37" s="46" t="s">
+      <c r="E37" s="43" t="s">
         <v>480</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="F37" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="G37" s="47" t="s">
+      <c r="G37" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="K37" s="42" t="str">
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="K37" s="39" t="str">
         <f>VLOOKUP(A37,原始數據!A:A,1,0)</f>
         <v>202604-035</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C38" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="45">
+      <c r="D38" s="42">
         <v>46135.696527777778</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F38" s="47" t="s">
+      <c r="F38" s="44" t="s">
         <v>482</v>
       </c>
-      <c r="G38" s="47" t="s">
+      <c r="G38" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H38" s="49" t="s">
+      <c r="H38" s="46" t="s">
         <v>483</v>
       </c>
-      <c r="I38" s="43"/>
-      <c r="K38" s="42" t="str">
+      <c r="I38" s="40"/>
+      <c r="K38" s="39" t="str">
         <f>VLOOKUP(A38,原始數據!A:A,1,0)</f>
         <v>202604-037</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" thickBot="1">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="44" t="s">
+      <c r="B39" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="45">
+      <c r="D39" s="42">
         <v>46137.640277777777</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F39" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="G39" s="47" t="s">
+      <c r="G39" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="K39" s="42" t="str">
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="K39" s="39" t="str">
         <f>VLOOKUP(A39,原始數據!A:A,1,0)</f>
         <v>202604-041</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C40" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="45">
+      <c r="D40" s="42">
         <v>46137.511805555558</v>
       </c>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F40" s="47" t="s">
+      <c r="F40" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="G40" s="47" t="s">
+      <c r="G40" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="K40" s="42" t="str">
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="K40" s="39" t="str">
         <f>VLOOKUP(A40,原始數據!A:A,1,0)</f>
         <v>202604-040</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" thickBot="1">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="45">
+      <c r="D41" s="42">
         <v>46137.47152777778</v>
       </c>
-      <c r="E41" s="46" t="s">
+      <c r="E41" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F41" s="47" t="s">
+      <c r="F41" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="G41" s="47" t="s">
+      <c r="G41" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="K41" s="42" t="str">
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="K41" s="39" t="str">
         <f>VLOOKUP(A41,原始數據!A:A,1,0)</f>
         <v>202604-039</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="44" t="s">
+      <c r="B42" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C42" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="45">
+      <c r="D42" s="42">
         <v>46137.455555555556</v>
       </c>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F42" s="47" t="s">
+      <c r="F42" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="G42" s="48">
+      <c r="G42" s="45">
         <v>137</v>
       </c>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="K42" s="42" t="str">
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="K42" s="39" t="str">
         <f>VLOOKUP(A42,原始數據!A:A,1,0)</f>
         <v>202604-038</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" thickBot="1">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="40" t="s">
         <v>487</v>
       </c>
-      <c r="B43" s="44" t="s">
+      <c r="B43" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="C43" s="43" t="s">
+      <c r="C43" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="45">
+      <c r="D43" s="42">
         <v>46139.679166666669</v>
       </c>
-      <c r="E43" s="46" t="s">
+      <c r="E43" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F43" s="47" t="s">
+      <c r="F43" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="G43" s="47" t="s">
+      <c r="G43" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="K43" s="42" t="e">
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="K43" s="39" t="e">
         <f>VLOOKUP(A43,原始數據!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="43">
+      <c r="A44" s="40">
         <v>20260400072</v>
       </c>
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C44" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="45">
+      <c r="D44" s="42">
         <v>46137.511805555558</v>
       </c>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="F44" s="47" t="s">
+      <c r="F44" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="G44" s="47" t="s">
+      <c r="G44" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="K44" s="42" t="e">
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="K44" s="39" t="e">
         <f>VLOOKUP(A44,原始數據!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" thickBot="1">
-      <c r="A45" s="43" t="s">
+      <c r="A45" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="44" t="s">
+      <c r="B45" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="43" t="s">
+      <c r="C45" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="42">
         <v>46139.730555555558</v>
       </c>
-      <c r="E45" s="46" t="s">
+      <c r="E45" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="F45" s="47" t="s">
+      <c r="F45" s="44" t="s">
         <v>490</v>
       </c>
-      <c r="G45" s="47" t="s">
+      <c r="G45" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="K45" s="42" t="str">
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="K45" s="39" t="str">
         <f>VLOOKUP(A45,原始數據!A:A,1,0)</f>
         <v>202604-044</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" thickBot="1">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="43"/>
-      <c r="D46" s="45">
+      <c r="C46" s="40"/>
+      <c r="D46" s="42">
         <v>46139.711111111108</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="44" t="s">
         <v>491</v>
       </c>
-      <c r="G46" s="48">
-        <v>2026</v>
-      </c>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="K46" s="42" t="str">
+      <c r="G46" s="45">
+        <v>2026</v>
+      </c>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="K46" s="39" t="str">
         <f>VLOOKUP(A46,原始數據!A:A,1,0)</f>
         <v>202604-043</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" thickBot="1">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="44" t="s">
+      <c r="B47" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="43" t="s">
+      <c r="C47" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="45">
+      <c r="D47" s="42">
         <v>46140.71875</v>
       </c>
-      <c r="E47" s="46" t="s">
+      <c r="E47" s="43" t="s">
         <v>445</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="F47" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="G47" s="47" t="s">
+      <c r="G47" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>

--- a/春大直_報修統計_2026.xlsx
+++ b/春大直_報修統計_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d14d3036a2a384b/_Ragic/portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AC74392-11EF-4CDF-99C6-88AB694D6825}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3E0886D-4782-4F34-8FE1-785029C4844B}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.1 報修統計" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="工作表1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">工作表1!$A$1:$K$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">原始數據!$A$1:$V$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -7965,13 +7966,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D55927-7564-41CF-96AB-8D7EDF6E8FB4}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.21875" style="39" customWidth="1"/>
     <col min="2" max="3" width="8.88671875" style="39"/>
     <col min="4" max="4" width="13.21875" style="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="8.88671875" style="39"/>
+    <col min="5" max="6" width="8.88671875" style="39"/>
+    <col min="7" max="7" width="14" style="39" customWidth="1"/>
+    <col min="8" max="10" width="8.88671875" style="39"/>
     <col min="11" max="11" width="11.21875" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8004,7 +8008,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1">
+    <row r="2" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A2" s="40" t="s">
         <v>295</v>
       </c>
@@ -8033,7 +8037,7 @@
         <v>202604-028</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1">
+    <row r="3" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A3" s="40" t="s">
         <v>298</v>
       </c>
@@ -8089,7 +8093,7 @@
         <v>202604-026</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1">
+    <row r="5" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A5" s="40" t="s">
         <v>303</v>
       </c>
@@ -8118,7 +8122,7 @@
         <v>202604-025</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1">
+    <row r="6" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A6" s="40" t="s">
         <v>307</v>
       </c>
@@ -8176,7 +8180,7 @@
         <v>202604-023</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1">
+    <row r="8" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A8" s="40" t="s">
         <v>314</v>
       </c>
@@ -8205,7 +8209,7 @@
         <v>202604-022</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1">
+    <row r="9" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A9" s="40" t="s">
         <v>317</v>
       </c>
@@ -8234,7 +8238,7 @@
         <v>202604-021</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1">
+    <row r="10" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A10" s="40" t="s">
         <v>320</v>
       </c>
@@ -8294,7 +8298,7 @@
         <v>202604-019</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1">
+    <row r="12" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A12" s="40" t="s">
         <v>328</v>
       </c>
@@ -8323,7 +8327,7 @@
         <v>202604-018</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1">
+    <row r="13" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A13" s="40" t="s">
         <v>333</v>
       </c>
@@ -8352,7 +8356,7 @@
         <v>202604-017</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1">
+    <row r="14" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A14" s="40" t="s">
         <v>336</v>
       </c>
@@ -8379,7 +8383,7 @@
         <v>202604-016</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1">
+    <row r="15" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A15" s="40" t="s">
         <v>340</v>
       </c>
@@ -8408,7 +8412,7 @@
         <v>202604-015</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1">
+    <row r="16" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A16" s="40" t="s">
         <v>343</v>
       </c>
@@ -8437,7 +8441,7 @@
         <v>202604-014</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1">
+    <row r="17" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A17" s="40" t="s">
         <v>348</v>
       </c>
@@ -8466,7 +8470,7 @@
         <v>202604-013</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1">
+    <row r="18" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A18" s="40" t="s">
         <v>350</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>202604-012</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1">
+    <row r="19" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A19" s="40" t="s">
         <v>354</v>
       </c>
@@ -8524,7 +8528,7 @@
         <v>202604-011</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1">
+    <row r="20" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A20" s="40" t="s">
         <v>358</v>
       </c>
@@ -8553,7 +8557,7 @@
         <v>202604-010</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1">
+    <row r="21" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A21" s="40" t="s">
         <v>361</v>
       </c>
@@ -8582,7 +8586,7 @@
         <v>202604-009</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1">
+    <row r="22" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A22" s="40" t="s">
         <v>364</v>
       </c>
@@ -8669,7 +8673,7 @@
         <v>202604-006</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1">
+    <row r="25" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A25" s="40" t="s">
         <v>374</v>
       </c>
@@ -8723,7 +8727,7 @@
         <v>202604-004</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" thickBot="1">
+    <row r="27" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A27" s="40" t="s">
         <v>382</v>
       </c>
@@ -8750,7 +8754,7 @@
         <v>202604-003</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" thickBot="1">
+    <row r="28" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A28" s="40" t="s">
         <v>385</v>
       </c>
@@ -8808,7 +8812,7 @@
         <v>202604-001</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1">
+    <row r="30" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A30" s="40" t="s">
         <v>293</v>
       </c>
@@ -8837,7 +8841,7 @@
         <v>202604-029</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" thickBot="1">
+    <row r="31" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A31" s="40" t="s">
         <v>285</v>
       </c>
@@ -8866,7 +8870,7 @@
         <v>202604-031</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1">
+    <row r="32" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A32" s="40" t="s">
         <v>290</v>
       </c>
@@ -8895,7 +8899,7 @@
         <v>202604-030</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1">
+    <row r="33" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A33" s="40" t="s">
         <v>281</v>
       </c>
@@ -8924,7 +8928,7 @@
         <v>202604-032</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1">
+    <row r="34" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A34" s="40" t="s">
         <v>125</v>
       </c>
@@ -8951,7 +8955,7 @@
         <v>202604-033</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" thickBot="1">
+    <row r="35" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A35" s="40" t="s">
         <v>119</v>
       </c>
@@ -8980,7 +8984,7 @@
         <v>202604-034</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1">
+    <row r="36" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A36" s="40" t="s">
         <v>101</v>
       </c>
@@ -9009,7 +9013,7 @@
         <v>202604-036</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1">
+    <row r="37" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A37" s="40" t="s">
         <v>104</v>
       </c>
@@ -9038,7 +9042,7 @@
         <v>202604-035</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1">
+    <row r="38" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A38" s="40" t="s">
         <v>95</v>
       </c>
@@ -9069,7 +9073,7 @@
         <v>202604-037</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1">
+    <row r="39" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A39" s="40" t="s">
         <v>74</v>
       </c>
@@ -9098,7 +9102,7 @@
         <v>202604-041</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1">
+    <row r="40" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A40" s="40" t="s">
         <v>81</v>
       </c>
@@ -9127,7 +9131,7 @@
         <v>202604-040</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" thickBot="1">
+    <row r="41" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A41" s="40" t="s">
         <v>84</v>
       </c>
@@ -9185,7 +9189,7 @@
         <v>202604-038</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1">
+    <row r="43" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A43" s="40" t="s">
         <v>487</v>
       </c>
@@ -9214,7 +9218,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1">
+    <row r="44" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A44" s="40">
         <v>20260400072</v>
       </c>
@@ -9243,7 +9247,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" thickBot="1">
+    <row r="45" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A45" s="40" t="s">
         <v>55</v>
       </c>
@@ -9299,7 +9303,7 @@
         <v>202604-043</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1">
+    <row r="47" spans="1:11" ht="15" hidden="1" thickBot="1">
       <c r="A47" s="40" t="s">
         <v>48</v>
       </c>
@@ -9325,6 +9329,19 @@
       <c r="I47" s="40"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K47" xr:uid="{70D55927-7564-41CF-96AB-8D7EDF6E8FB4}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="$1,600"/>
+        <filter val="$137"/>
+        <filter val="$142"/>
+        <filter val="$2,026"/>
+        <filter val="$31,300"/>
+        <filter val="$38"/>
+        <filter val="$499"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/春大直_報修統計_2026.xlsx
+++ b/春大直_報修統計_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d14d3036a2a384b/_Ragic/portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3E0886D-4782-4F34-8FE1-785029C4844B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_71875BABB67AE4F8E5FFFBEEA8B38370D980C640" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{083D0F3B-E5E3-4915-8AC6-423853EB319F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2278,14 +2278,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="14" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5" customHeight="1">
+    <row r="1" spans="1:17" ht="13.5" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2303,7 +2303,7 @@
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
     </row>
-    <row r="2" spans="1:14" ht="24" customHeight="1">
+    <row r="2" spans="1:17" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+    <row r="3" spans="1:17" ht="19.5" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="19.5" customHeight="1">
+    <row r="4" spans="1:17" ht="19.5" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
@@ -2436,8 +2436,12 @@
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4)</f>
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="19.5" customHeight="1">
+      <c r="Q4">
+        <f>59+1911</f>
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="19.5" customHeight="1">
       <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
@@ -2482,7 +2486,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="19.5" customHeight="1">
+    <row r="6" spans="1:17" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
@@ -2526,7 +2530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="19.5" customHeight="1">
+    <row r="7" spans="1:17" ht="19.5" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>20</v>
       </c>
@@ -2571,7 +2575,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="19.5" customHeight="1">
+    <row r="8" spans="1:17" ht="19.5" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
@@ -2616,7 +2620,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="19.5" customHeight="1">
+    <row r="9" spans="1:17" ht="19.5" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
@@ -2661,7 +2665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="19.5" customHeight="1">
+    <row r="10" spans="1:17" ht="19.5" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>23</v>
       </c>
@@ -2705,7 +2709,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="19.5" customHeight="1">
+    <row r="11" spans="1:17" ht="19.5" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2750,7 +2754,7 @@
         <v>4.0666666666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5" customHeight="1">
+    <row r="13" spans="1:17" ht="13.5" customHeight="1">
       <c r="A13" s="48" t="s">
         <v>25</v>
       </c>
